--- a/artfynd/A 39994-2020 artfynd.xlsx
+++ b/artfynd/A 39994-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39994-2020 artfynd.xlsx
+++ b/artfynd/A 39994-2020 artfynd.xlsx
@@ -6601,7 +6601,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117170553</v>
+        <v>117168801</v>
       </c>
       <c r="B49" t="n">
         <v>57287</v>
@@ -6637,7 +6637,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6646,13 +6646,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443136</v>
+        <v>443333</v>
       </c>
       <c r="R49" t="n">
-        <v>7162340</v>
+        <v>7162128</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117168801</v>
+        <v>117170553</v>
       </c>
       <c r="B50" t="n">
         <v>57287</v>
@@ -6744,7 +6744,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6753,13 +6753,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443333</v>
+        <v>443136</v>
       </c>
       <c r="R50" t="n">
-        <v>7162128</v>
+        <v>7162340</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 39994-2020 artfynd.xlsx
+++ b/artfynd/A 39994-2020 artfynd.xlsx
@@ -6604,7 +6604,7 @@
         <v>117168801</v>
       </c>
       <c r="B49" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>117170553</v>
       </c>
       <c r="B50" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
